--- a/data/000625_长安汽车_财务数据.xlsx
+++ b/data/000625_长安汽车_财务数据.xlsx
@@ -11565,7 +11565,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -18829,7 +18829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -18859,8 +18859,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18907,22 +18905,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -18932,75 +18930,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -19034,58 +19022,52 @@
         <v>6.530044483510713</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>-0.3888227924388964</v>
+      <c r="J2" s="3" t="n">
+        <v>59.29677964510376</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>59.29677964510376</v>
-      </c>
-      <c r="L2" s="3" t="n">
         <v>1.1000766743341</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="L2" s="6" t="n">
         <v>0.9783311664499782</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>145.6808064032478</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>2.575077596052261</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>139.8016124065156</v>
-      </c>
-      <c r="P2" s="3" t="n">
         <v>10.7753678150575</v>
       </c>
+      <c r="P2" s="6" t="n">
+        <v>0.7374184748586049</v>
+      </c>
       <c r="Q2" s="3" t="n">
-        <v>33.40953238709272</v>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v>0.7374184748586049</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>1.190073059141035</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="6" t="n">
+      <c r="V2" s="6" t="n">
         <v>0.2225445369719537</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="W2" s="3" t="n">
         <v>-2358000000</v>
       </c>
+      <c r="X2" s="3" t="n">
+        <v>1.005087163498751</v>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>+/+/−</t>
+        </is>
+      </c>
       <c r="Z2" s="3" t="n">
-        <v>1.005087163498751</v>
+        <v>1.98775505857281</v>
       </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>+/+/−</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>1.98775505857281</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19121,64 +19103,58 @@
       <c r="I3" s="3" t="n">
         <v>3.270315358895466</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>-0.6561173508759555</v>
+      <c r="J3" s="3" t="n">
+        <v>55.27632508833922</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>55.27632508833922</v>
+        <v>1.149332454260755</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.149332454260755</v>
+        <v>1.063879274032562</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.063879274032562</v>
+        <v>123.5952215409898</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>2.603546960248926</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>138.2729044248083</v>
-      </c>
-      <c r="P3" s="3" t="n">
         <v>13.60434758513283</v>
       </c>
+      <c r="P3" s="6" t="n">
+        <v>0.7525779404366167</v>
+      </c>
       <c r="Q3" s="3" t="n">
-        <v>26.46212894423669</v>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v>0.7525779404366167</v>
-      </c>
+        <v>1.242859775268844</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.242859775268844</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="3" t="n">
         <v>1.871298360857805</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="T3" s="3" t="n">
         <v>-29.8557789874562</v>
       </c>
-      <c r="W3" s="6" t="n">
+      <c r="U3" s="6" t="n">
         <v>-0.3614684067223592</v>
       </c>
-      <c r="X3" s="6" t="n">
+      <c r="V3" s="6" t="n">
         <v>-0.1557896611883331</v>
       </c>
-      <c r="Y3" s="3" t="n">
+      <c r="W3" s="3" t="n">
         <v>-4432000000</v>
       </c>
+      <c r="X3" s="3" t="n">
+        <v>1.061463058122458</v>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>−/+/−</t>
+        </is>
+      </c>
       <c r="Z3" s="3" t="n">
-        <v>1.061463058122458</v>
+        <v>2.052216039867227</v>
       </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>−/+/−</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>2.052216039867227</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19214,64 +19190,58 @@
       <c r="I4" s="3" t="n">
         <v>4.803728518039019</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>-0.6441526039054811</v>
+      <c r="J4" s="3" t="n">
+        <v>50.63269475553274</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>50.63269475553274</v>
-      </c>
-      <c r="L4" s="3" t="n">
         <v>1.001227988878591</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="L4" s="6" t="n">
         <v>0.8873030583873958</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>102.5632136589171</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>2.504940884488986</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>143.7159664043093</v>
-      </c>
-      <c r="P4" s="3" t="n">
         <v>14.41544413555046</v>
       </c>
+      <c r="P4" s="6" t="n">
+        <v>0.6642647348359333</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>24.97321599077137</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0.6642647348359333</v>
-      </c>
+        <v>1.251264893644805</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="3" t="n">
-        <v>1.251264893644805</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
+        <v>-17.13980356039699</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-89.96510124497513</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>-17.13980356039699</v>
+        <v>-11.90671378091873</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>-89.96510124497513</v>
+        <v>-5.373539208064851</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>-11.90671378091873</v>
+        <v>-10375000000</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>-5.373539208064851</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>-10375000000</v>
+        <v>1.157873343432577</v>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>−/−/−</t>
+        </is>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>1.157873343432577</v>
+        <v>1.859206569695494</v>
       </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>−/−/−</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>1.859206569695494</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19307,64 +19277,58 @@
       <c r="I5" s="3" t="n">
         <v>4.489061203976244</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>-0.2703432948914427</v>
+      <c r="J5" s="3" t="n">
+        <v>54.99349498550458</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>54.99349498550458</v>
-      </c>
-      <c r="L5" s="3" t="n">
         <v>1.007596530782199</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="L5" s="6" t="n">
         <v>0.9390449495257246</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>122.1901033368234</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>2.845721863681548</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>126.5056872192925</v>
-      </c>
-      <c r="P5" s="3" t="n">
         <v>17.50006250600579</v>
       </c>
+      <c r="P5" s="6" t="n">
+        <v>0.738807207866629</v>
+      </c>
       <c r="Q5" s="3" t="n">
-        <v>20.57135509524339</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0.738807207866629</v>
-      </c>
+        <v>1.521121420669683</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>1.521121420669683</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
+        <v>6.481277291621527</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-466.2262434519849</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>6.481277291621527</v>
+        <v>4.415492731765235</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-466.2262434519849</v>
+        <v>-1.465385703657986</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>4.415492731765235</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>-1.465385703657986</v>
-      </c>
-      <c r="Y5" s="3" t="n">
         <v>-902000000</v>
       </c>
-      <c r="Z5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.9997557182038614</v>
       </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>1.627288952903259</v>
+      </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>1.627288952903259</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19400,64 +19364,58 @@
       <c r="I6" s="3" t="n">
         <v>3.416135562035323</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>-0.2487886192340058</v>
+      <c r="J6" s="3" t="n">
+        <v>54.77952056821545</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>54.77952056821545</v>
+        <v>1.164507213266659</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1.164507213266659</v>
+        <v>1.069161088300609</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.069161088300609</v>
+        <v>121.1387434554974</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>2.9081811010396</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>123.7887144893794</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>18.32077538234186</v>
       </c>
+      <c r="P6" s="6" t="n">
+        <v>0.7834422892745111</v>
+      </c>
       <c r="Q6" s="3" t="n">
-        <v>19.64982335556492</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0.7834422892745111</v>
-      </c>
+        <v>1.38069575820763</v>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="3" t="n">
-        <v>1.38069575820763</v>
-      </c>
-      <c r="T6" s="4" t="inlineStr"/>
+        <v>19.78929173901845</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>224.1341986037403</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>19.78929173901845</v>
+        <v>21.15205343331593</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>224.1341986037403</v>
+        <v>3.246486038064851</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>21.15205343331593</v>
+        <v>7716000000</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>3.246486038064851</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>7716000000</v>
+        <v>1.029166203307872</v>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/+/+</t>
+        </is>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>1.029166203307872</v>
+        <v>1.826551624826338</v>
       </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/+/+</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>1.826551624826338</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19493,64 +19451,58 @@
       <c r="I7" s="3" t="n">
         <v>3.343129560864803</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>-0.7427327889717547</v>
+      <c r="J7" s="3" t="n">
+        <v>58.74081459325726</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>58.74081459325726</v>
+        <v>1.197524537821751</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.197524537821751</v>
+        <v>1.107480258057735</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.107480258057735</v>
+        <v>142.3728206780511</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>3.724737042548179</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>96.65111815617341</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>15.98947871449185</v>
       </c>
+      <c r="P7" s="6" t="n">
+        <v>0.8289657999530887</v>
+      </c>
       <c r="Q7" s="3" t="n">
-        <v>22.51480529341578</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0.8289657999530887</v>
-      </c>
+        <v>1.281983505908066</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>1.281983505908066</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>24.33181657863447</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>9.601386585888324</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>24.33181657863447</v>
+        <v>14.49287616792794</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>9.601386585888324</v>
+        <v>6.373642989723514</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>14.49287616792794</v>
+        <v>20962000000</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>6.373642989723514</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>20962000000</v>
+        <v>1.222624166298429</v>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>1.222624166298429</v>
+        <v>1.827393934503929</v>
       </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>1.827393934503929</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19586,64 +19538,58 @@
       <c r="I8" s="3" t="n">
         <v>3.559045716001047</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>-0.8389952276620025</v>
+      <c r="J8" s="3" t="n">
+        <v>56.89871207608406</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>56.89871207608406</v>
+        <v>1.354529651401956</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.354529651401956</v>
+        <v>1.277259517774917</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.277259517774917</v>
+        <v>132.0116284611352</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>3.738852749276144</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.28622043745834</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>17.74697478378826</v>
       </c>
+      <c r="P8" s="6" t="n">
+        <v>0.861617629064785</v>
+      </c>
       <c r="Q8" s="3" t="n">
-        <v>20.28514743419016</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0.861617629064785</v>
-      </c>
+        <v>1.255101690185078</v>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="3" t="n">
-        <v>1.255101690185078</v>
-      </c>
-      <c r="T8" s="4" t="inlineStr"/>
+        <v>15.32309225564482</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>114.8878257185361</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>15.32309225564482</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>114.8878257185361</v>
+        <v>7.860861858867841</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>0.7315662884722787</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>7.860861858867841</v>
-      </c>
-      <c r="X8" s="6" t="n">
-        <v>0.7315662884722787</v>
-      </c>
-      <c r="Y8" s="3" t="n">
         <v>4261000000</v>
       </c>
+      <c r="X8" s="3" t="n">
+        <v>1.01126683418907</v>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
       <c r="Z8" s="3" t="n">
-        <v>1.01126683418907</v>
+        <v>2.109993422482498</v>
       </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>2.109993422482498</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19679,64 +19625,58 @@
       <c r="I9" s="3" t="n">
         <v>3.952369659629442</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.5930980447005809</v>
+      <c r="J9" s="3" t="n">
+        <v>60.72850224271841</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>60.72850224271841</v>
+        <v>1.268270711649667</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1.268270711649667</v>
+        <v>1.137835507899146</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1.137835507899146</v>
+        <v>154.6376015960794</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>3.830903596672153</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>93.97260748423074</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>15.04550019922235</v>
       </c>
+      <c r="P9" s="6" t="n">
+        <v>0.8999923065074653</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>23.92741984202074</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0.8999923065074653</v>
-      </c>
+        <v>1.298631452137195</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>1.298631452137195</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
+        <v>24.77866629229395</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>22.68388660149535</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>24.77866629229395</v>
+        <v>30.21040883539086</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>22.68388660149535</v>
+        <v>2.090213747206105</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>30.21040883539086</v>
+        <v>17037000000</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>2.090213747206105</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>17037000000</v>
+        <v>1.113691699195194</v>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1.113691699195194</v>
+        <v>1.940004665533251</v>
       </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>1.940004665533251</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19772,64 +19712,58 @@
       <c r="I10" s="3" t="n">
         <v>4.072699621140965</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>-0.5849618506605019</v>
+      <c r="J10" s="3" t="n">
+        <v>62.0114522885362</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>62.0114522885362</v>
+        <v>1.203004666672548</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.203004666672548</v>
+        <v>1.052321426996127</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.052321426996127</v>
+        <v>163.2351639458277</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>3.58753122917158</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>100.3475585306974</v>
-      </c>
-      <c r="P10" s="3" t="n">
         <v>10.3270463414057</v>
       </c>
+      <c r="P10" s="6" t="n">
+        <v>0.8019954572022825</v>
+      </c>
       <c r="Q10" s="3" t="n">
-        <v>34.85991909967525</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>0.8019954572022825</v>
-      </c>
+        <v>1.195141368728115</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>1.195141368728115</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
+        <v>5.575317533373155</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>-35.75837312593823</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>5.575317533373155</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>-35.75837312593823</v>
+        <v>9.463588033927344</v>
+      </c>
+      <c r="V10" s="6" t="n">
+        <v>0.794374403594896</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>9.463588033927344</v>
-      </c>
-      <c r="X10" s="6" t="n">
-        <v>0.794374403594896</v>
-      </c>
-      <c r="Y10" s="3" t="n">
         <v>-19000000</v>
       </c>
+      <c r="X10" s="3" t="n">
+        <v>1.100736618859114</v>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
       <c r="Z10" s="3" t="n">
-        <v>1.100736618859114</v>
+        <v>1.765293086848585</v>
       </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>1.765293086848585</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19866,63 +19800,57 @@
         <v>4.364394809067896</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-1.464790884761207</v>
+        <v>59.60553998058741</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>59.60553998058741</v>
-      </c>
-      <c r="L11" s="3" t="n">
         <v>1.212089497355246</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>0.9997737108590503</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>147.5586997621516</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>3.806247914124214</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>94.5813326200096</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>8.149539409585595</v>
       </c>
+      <c r="P11" s="6" t="n">
+        <v>0.7978021685450065</v>
+      </c>
       <c r="Q11" s="3" t="n">
-        <v>44.17427561324058</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0.7978021685450065</v>
-      </c>
+        <v>1.238098790405251</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>1.238098790405251</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>2.671188012946456</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>-48.10941560241319</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>2.671188012946456</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>-48.10941560241319</v>
+        <v>-2.501345067445511</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>0.5796384317792738</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-2.501345067445511</v>
-      </c>
-      <c r="X11" s="6" t="n">
-        <v>0.5796384317792738</v>
-      </c>
-      <c r="Y11" s="3" t="n">
         <v>-2843000000</v>
       </c>
+      <c r="X11" s="3" t="n">
+        <v>1.046092714414778</v>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
       <c r="Z11" s="3" t="n">
-        <v>1.046092714414778</v>
+        <v>1.815350832288974</v>
       </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>1.815350832288974</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>

--- a/data/000625_长安汽车_财务数据.xlsx
+++ b/data/000625_长安汽车_财务数据.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务分析指标" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据质量校验" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并报表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务指标表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40184,4 +40185,2123 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>营业利润率</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>净利润率</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>净资产收益率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>存货周转率</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>总资产周转率</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>应收账款周转率</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>流动比率</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>速动比率</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>利息保障倍数</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>资产负债率</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>货币资金占比</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>营业收入增长率</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>营业利润增长率</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>净利润增长率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2016Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.003565809766810757</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.1285913742521257</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1375668374378764</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.06632796871935484</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.37315127833241</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1921306378170672</v>
+      </c>
+      <c r="H2" t="n">
+        <v>13.96732146309137</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.054433627798562</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8662958102364211</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6117441026290248</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1974617040131662</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.7537922665374767</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.7363581530996952</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.7411366214009767</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2016Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-0.000205681529599433</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1452897031931518</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1529743552692288</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1487609168503041</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.740442542707474</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3763318170912455</v>
+      </c>
+      <c r="H3" t="n">
+        <v>26.03764576090909</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.015725992081761</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8094282294448026</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6169628923637659</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2236931681312121</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8513917475228385</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.091805605595644</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.058748054420994</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2016Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.0029098983784559</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.138235665013257</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1440880689442073</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2040859745849375</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.5118912204634</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5467395835072438</v>
+      </c>
+      <c r="H4" t="n">
+        <v>35.7618385947365</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.055367663102771</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.870336024438141</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6141843407740166</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2494881631517224</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.497328390543913</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.4246307980607382</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4103485253401062</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2017年报</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.01762000074159498</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.08938170707918196</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.09009172105218165</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1647447019705468</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11.6633749172067</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7740257728906903</v>
+      </c>
+      <c r="H5" t="n">
+        <v>48.12764221495939</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.149332454260755</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.043697232752779</v>
+      </c>
+      <c r="K5" t="n">
+        <v>148.9605692492768</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5527632508833922</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2132579505300353</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.4925702067413469</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.03492001864153471</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.06676368347606731</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2017Q1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.003874739323836307</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1379134180802472</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.135326395623708</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05132723711424601</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.40473345037781</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.16222183288501</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.345535526022674</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.13788478415658</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9508701627725984</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5904882983866636</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2536215016025928</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.7791899539786352</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-0.6592964132326817</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.668322157723362</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017Q2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.009433416244367665</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1394068952231214</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1390979871391171</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1014712859092357</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.266793981953995</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3064724889779292</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15.50968944278253</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.186441886160317</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9718786755533378</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5812290856892517</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2598920611839713</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8992622364333518</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.9198295226185651</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.9521953046899487</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2017Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.02067829991301928</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1116391605286313</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1137263284692608</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.127093692642665</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.086201950476698</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4859746288552503</v>
+      </c>
+      <c r="H8" t="n">
+        <v>26.40204360697125</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.20409704339071</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9774043022828044</v>
+      </c>
+      <c r="K8" t="n">
+        <v>128.6003309798878</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5578037727895457</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2298546642523879</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5327329550435889</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2274358462812576</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2531604165243018</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2018年报</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.04183110915888899</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.003038365084424321</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01091068255050009</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01470525673244548</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.338416896571353</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6701262497197121</v>
+      </c>
+      <c r="H9" t="n">
+        <v>38.94171535375624</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.001227988878591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8672381835032438</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-16.21693790054585</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5063269475553274</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1067612232455155</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2890676272607819</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1.035083191700697</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0.8763293614022694</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2018Q1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.0189283003998364</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.06923559402109397</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.06782380333563778</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.02923505803075178</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.053178882832721</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.199454256716952</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11.54355173970003</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.208738526299378</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.080077173425837</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5446410242054383</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2198551779482298</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.6981709051665137</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-7.87781622451238</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.8762526610236359</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2018Q2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.02054476367999225</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.04645533914481395</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.04538027912164588</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.03343455981970005</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.370842098129685</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.3434179334901266</v>
+      </c>
+      <c r="H11" t="n">
+        <v>17.89298804720883</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.168415180965866</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.045482825942374</v>
+      </c>
+      <c r="K11" t="n">
+        <v>119.3021151700541</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.530051488382747</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2396948541494458</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.7811844952884346</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.1951299180432893</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1917740614358163</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2018Q3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.02754554246406071</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.02369337431978277</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0234910530150217</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.02469230146721016</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.171040974532271</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5111522679657124</v>
+      </c>
+      <c r="H12" t="n">
+        <v>23.24086638235898</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.112635501355014</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9306039488966318</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5059115642664694</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1652596544983887</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3986447015310557</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.2866565380040804</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.2759930641948505</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2019年报</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.02776410809141039</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.02984773456628551</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.03752564193067937</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.05822147970237244</v>
+      </c>
+      <c r="F13" t="n">
+        <v>14.77703852340122</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7343650345183136</v>
+      </c>
+      <c r="H13" t="n">
+        <v>44.09446916507183</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.007596530782199</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9263705238356387</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-51.53359077853058</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5499349498550458</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1031172848991467</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4161062522889807</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-2.783940225883637</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-3.262150450437928</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2019Q1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.1061722298995955</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.1277129699744774</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.1313685341065195</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.04739340144507494</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.698705047329504</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1654705360908396</v>
+      </c>
+      <c r="H14" t="n">
+        <v>38.20513270286396</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.027849726087056</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8624246452884682</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5374946540519678</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1254237641732817</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.7732432181193244</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.02974940990840369</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.2061773096539048</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2019Q2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.08480464912706931</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.07141856509165037</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.07511306553589733</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.05067390026263997</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.444667811062579</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3169575006560716</v>
+      </c>
+      <c r="H15" t="n">
+        <v>29.69759452966203</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.037128531246178</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.872226978109331</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-74.61953734790926</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5264277002450107</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.113708728642511</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.8663088635577265</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.04366143140949941</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.06710622092326912</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2019Q3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.06053189596693853</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.05576151596575919</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.05910692954867301</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.06080672612108751</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8.320379792517173</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.4861680420678247</v>
+      </c>
+      <c r="H16" t="n">
+        <v>22.1425383891092</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.077638623095371</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9146338509241539</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.5323033556758152</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1130859522093236</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.5101002156787837</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.1790418524708426</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.188307073113728</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2020年报</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.01206115401163954</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03103042212134957</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03888674371916748</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.06855681008393656</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14.5504083982676</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.8007645791581918</v>
+      </c>
+      <c r="H17" t="n">
+        <v>40.23099150646051</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.164507213266659</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.061796047481348</v>
+      </c>
+      <c r="K17" t="n">
+        <v>57.22431908502275</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5477952056821545</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2705956961062022</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8744265366046624</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-2.043089407791894</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-2.233194566287341</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2020Q1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.09525134919425393</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.05974243715161523</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.05392302224858127</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.01286693013018258</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.472778493539633</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1083042450722086</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.822798319909365</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.080378029381492</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9574716945822027</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5321306004219011</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1432259689556374</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.8632530828005359</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.7367230753575451</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.8103773586231903</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2020Q2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.0532199258329844</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0857713461655385</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.07936214972805049</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.05697010251948507</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8.303582217128428</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3309857634762854</v>
+      </c>
+      <c r="H19" t="n">
+        <v>15.87105179331881</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.161611191922649</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.061585522375289</v>
+      </c>
+      <c r="K19" t="n">
+        <v>139.0113741763931</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.5469543394097391</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1685375770899399</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.834783629132818</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.069857534296768</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.172142313996211</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2020Q3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.03528062318994651</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.05690244307836334</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.06239625184308629</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.07397839568838004</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12.99869773090051</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.521257950345053</v>
+      </c>
+      <c r="H20" t="n">
+        <v>24.99063877088387</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.151521231577411</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.050124033270101</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5740164191826298</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.1931182988650128</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.7034398693580974</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.1300964079133067</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.3392815523803074</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021年报</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.02512152157836167</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.03548085273196391</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.03427956856670942</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.06877488108317927</v>
+      </c>
+      <c r="F21" t="n">
+        <v>17.50948980171678</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8518340536097383</v>
+      </c>
+      <c r="H21" t="n">
+        <v>54.7044106332206</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.197524537821751</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.064895476106009</v>
+      </c>
+      <c r="K21" t="n">
+        <v>83.60610302482102</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5874081459325726</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.3838558398877442</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.8828599198540059</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.1740352771717735</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.03441511016492327</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021Q1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.01622597744029475</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.02435859754121846</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.02669669851046059</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.01543847937329873</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5.732832281961427</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.2431894485564592</v>
+      </c>
+      <c r="H22" t="n">
+        <v>16.55158698012403</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.227827453771668</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.163233833059003</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.5709162506152873</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.3067060450507466</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.6953894903899036</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.7908763674179289</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.7627713743726641</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.01734960220119219</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.03235865814285738</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.03178643989729837</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0317315988072519</v>
+      </c>
+      <c r="F23" t="n">
+        <v>13.56330605845406</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.4394296076106126</v>
+      </c>
+      <c r="H23" t="n">
+        <v>29.70684378711483</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.236124738705687</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.172475576980504</v>
+      </c>
+      <c r="K23" t="n">
+        <v>70.67471225875373</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5838354106302411</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.3657958883318769</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.7730059982873916</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.355311913452117</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.111030642235744</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021Q3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.02502888351688537</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.03986160413243328</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.03872613774321682</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.05458957429647805</v>
+      </c>
+      <c r="F24" t="n">
+        <v>16.08859899024065</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.6037514088807661</v>
+      </c>
+      <c r="H24" t="n">
+        <v>37.69609998361257</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.245656089984539</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.159784967589112</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.5782714177407127</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3944200151630023</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.3947348678131892</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.7181296246903539</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.6992369947913415</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022年报</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.07234911910675679</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.06295717437002937</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0638749951270848</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.1318030313905695</v>
+      </c>
+      <c r="F25" t="n">
+        <v>19.85005315091326</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.872482823002781</v>
+      </c>
+      <c r="H25" t="n">
+        <v>42.98222760914569</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.354529651401956</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.267307156411311</v>
+      </c>
+      <c r="K25" t="n">
+        <v>157.8034183794294</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5689871207608406</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.3665208252025005</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.5309800541560654</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.418020556982956</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.525202594364361</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022Q1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.06606396233768386</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1307131123324997</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1310935199576263</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.07322488960743168</v>
+      </c>
+      <c r="F26" t="n">
+        <v>5.487575625337752</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.2407345223450408</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8.448590561659131</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.285382416011437</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.150753285313686</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.5666978272570182</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.3577164952834198</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.7148450295636912</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.4079547874283918</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.4147636530768586</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022Q2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.05839330717482716</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1005106621436348</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1032111555428984</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.09623806617454736</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8.213715309000076</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.4040738271649477</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12.9845233862084</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.284280093532533</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.131813663030846</v>
+      </c>
+      <c r="K27" t="n">
+        <v>318.8021550358808</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.5618966659942944</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.3848514537648042</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.636215946882938</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.2581534116703061</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.2882081330190218</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.05310686741358261</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0775519567626686</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.08043298510792961</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.11264161180645</v>
+      </c>
+      <c r="F28" t="n">
+        <v>11.35176165154575</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.6042443159506844</v>
+      </c>
+      <c r="H28" t="n">
+        <v>23.18077796934818</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.294207723035952</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.160572569906791</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.5690037927554891</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.3589547305055847</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.5086837706463223</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.1640693241330218</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.1757250330031821</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023年报</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.04092183624446233</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.06905244529150455</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0628026640426297</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1694776586968393</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14.03349387537718</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.906337911898606</v>
+      </c>
+      <c r="H29" t="n">
+        <v>48.97158331347143</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.268270711649667</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.13504586445045</v>
+      </c>
+      <c r="K29" t="n">
+        <v>160.1188805014687</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.607285022427184</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.341119308411903</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.7726400354202598</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.5783628702236776</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.3840903264205533</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.04365909524034384</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1981971436996314</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.1936500100811222</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.09868126425010795</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.887245053098899</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1897227116929285</v>
+      </c>
+      <c r="H30" t="n">
+        <v>16.24640089692054</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.291184515043131</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.178170020042743</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.5760242147160687</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.3615608612995307</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.7716019926965493</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.3444427277972044</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.29574203433792</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.02217358043196194</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1078578535801441</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.106379443022656</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.1114254627714483</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6.508451094779207</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3752032292511072</v>
+      </c>
+      <c r="H31" t="n">
+        <v>30.32743638296365</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.269915459587529</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.152366593075225</v>
+      </c>
+      <c r="K31" t="n">
+        <v>192.8766434548055</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.5889492722566045</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.3770779402604675</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.895240171752449</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.03137983286922053</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.04112875481250788</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.027062143283894</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.08303513997719816</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08079386296138685</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.1429746032952836</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10.5557752556244</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.5988655394742799</v>
+      </c>
+      <c r="H32" t="n">
+        <v>42.05453534111154</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.262621859396053</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.156792422921455</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.6040358840635698</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.3873418536522551</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.6522041788445689</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.2719612036348411</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.2548285102542742</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2024年报</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.01253899625493915</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.04147013126756545</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.03821485366452554</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.09970195618071018</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11.78189671674771</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.8097055056355913</v>
+      </c>
+      <c r="H33" t="n">
+        <v>52.65634884234382</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.203004666672548</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.047848831567526</v>
+      </c>
+      <c r="K33" t="n">
+        <v>57.02341065444433</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.6201145228853618</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.3083182813881096</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.4761895150922963</v>
+      </c>
+      <c r="O33" t="n">
+        <v>-0.26274860277839</v>
+      </c>
+      <c r="P33" t="n">
+        <v>-0.3017741170846142</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.009343484933793</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.02155845409877473</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.02310658203016415</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.01546163078198641</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.517034254475465</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1857117862119749</v>
+      </c>
+      <c r="H34" t="n">
+        <v>11.0931005637573</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.285534850402818</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.15704514900841</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.6024014820334928</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.3677164403906606</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-0.7682181189764885</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.8795070357811677</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.859853262974885</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.008700876145613656</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.02978522280913103</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.02928421106125234</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.03906876439094384</v>
+      </c>
+      <c r="F35" t="n">
+        <v>5.760658621547434</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.4060785279833065</v>
+      </c>
+      <c r="H35" t="n">
+        <v>24.48855720516757</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.257426928605654</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.113919501677048</v>
+      </c>
+      <c r="K35" t="n">
+        <v>58.8217557782172</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.6048835694686155</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.3787008466704391</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.072284453765727</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.863074221208588</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.626317265089529</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.009764560367465536</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.02532265867760664</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.02443122201258887</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.04958820543623556</v>
+      </c>
+      <c r="F36" t="n">
+        <v>8.366096213147294</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.5982326640304833</v>
+      </c>
+      <c r="H36" t="n">
+        <v>30.75803085009287</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.262809812580556</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.12620702770089</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.5935764229236098</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.3812161014180226</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.4462430154742674</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.2295599895428784</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.2065711492552254</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025年报</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.01611586278347299</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.02261448324015763</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.01931399770177437</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.05434391723561299</v>
+      </c>
+      <c r="F37" t="n">
+        <v>9.222496887293667</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.8484277109024125</v>
+      </c>
+      <c r="H37" t="n">
+        <v>38.94094832621869</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.212089497355246</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9951347834695783</v>
+      </c>
+      <c r="K37" t="n">
+        <v>35.79866744821766</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.5960553998058741</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.2661693625869009</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.4780137036973224</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.3199449772051148</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.168437389733997</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.0222794646668435</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.03638197585279009</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.03557953337741964</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.01739918214418934</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.597107352229528</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1695869967171381</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7.411713407836841</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.235126194678317</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.04472026926675</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.5968875527120111</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.3007848649622074</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.7917034881177306</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-0.6648944578992597</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.6162838573686671</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.01394123044602757</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.02896798695094464</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.02466118552168269</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.02971816719850061</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.950719510419997</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.3824519859474447</v>
+      </c>
+      <c r="H39" t="n">
+        <v>12.48026618372049</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.220916812851999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.02034669005632</v>
+      </c>
+      <c r="K39" t="n">
+        <v>56.31786742676996</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.5665719707478388</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.293131956543451</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.127929188724617</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.6942956924859172</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.4749281825445728</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.008781484810970297</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.02087236028152718</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.01866089094497903</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.03989105716186397</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.43678679166516</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.6282662392688927</v>
+      </c>
+      <c r="H40" t="n">
+        <v>16.60321967884715</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.221407351377424</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.01080891461396</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.5755050369013629</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.2975865969940203</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.5810347344819218</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.1391860487785541</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.1963543575166258</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/000625_长安汽车_财务数据.xlsx
+++ b/data/000625_长安汽车_财务数据.xlsx
@@ -40193,7 +40193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40272,6 +40272,21 @@
           <t>净利润增长率</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>有息负债率</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>经营现金流/营收</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>权益乘数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40324,6 +40339,15 @@
       <c r="P2" t="n">
         <v>-0.7411366214009767</v>
       </c>
+      <c r="Q2" t="n">
+        <v>0.02258724733088576</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.08351537545305297</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.560038891589694</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40376,6 +40400,15 @@
       <c r="P3" t="n">
         <v>1.058748054420994</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0.02244472606541753</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1290718563263046</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.594749571975976</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -40428,6 +40461,15 @@
       <c r="P4" t="n">
         <v>0.4103485253401062</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0.02173210757518535</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1211222504152023</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.576843291418035</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -40480,6 +40522,15 @@
       <c r="P5" t="n">
         <v>-0.06676368347606731</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0.001929120376914017</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.01403535869859319</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.22956364629509</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -40532,6 +40583,15 @@
       <c r="P6" t="n">
         <v>-0.668322157723362</v>
       </c>
+      <c r="Q6" t="n">
+        <v>0.01975917148638244</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.2448563925971413</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.429662178329817</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -40584,6 +40644,15 @@
       <c r="P7" t="n">
         <v>0.9521953046899487</v>
       </c>
+      <c r="Q7" t="n">
+        <v>0.002008171844560648</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1478160780508248</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.378780487804878</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -40636,6 +40705,15 @@
       <c r="P8" t="n">
         <v>0.2531604165243018</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0.001932648329644852</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.01454370648770118</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.252557296387414</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -40688,6 +40766,15 @@
       <c r="P9" t="n">
         <v>-0.8763293614022694</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.002102858090256608</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.05862898047186122</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.021602335387609</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -40740,6 +40827,15 @@
       <c r="P10" t="n">
         <v>0.8762526610236359</v>
       </c>
+      <c r="Q10" t="n">
+        <v>0.001711582031614505</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1317292156960618</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.188445751393739</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40792,6 +40888,15 @@
       <c r="P11" t="n">
         <v>0.1917740614358163</v>
       </c>
+      <c r="Q11" t="n">
+        <v>0.001986071247174114</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1234750363420843</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.122181126492656</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -40844,6 +40949,15 @@
       <c r="P12" t="n">
         <v>-0.2759930641948505</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0.002034910454857626</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.01853499020570967</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.018404384636711</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -40896,6 +41010,15 @@
       <c r="P13" t="n">
         <v>-3.262150450437928</v>
       </c>
+      <c r="Q13" t="n">
+        <v>0.002922646670149667</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.0549895392058062</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.217157263559553</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -40948,6 +41071,15 @@
       <c r="P14" t="n">
         <v>-0.2061773096539048</v>
       </c>
+      <c r="Q14" t="n">
+        <v>0.002242690393983331</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2035863353733134</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.157320311445159</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -41000,6 +41132,15 @@
       <c r="P15" t="n">
         <v>0.06710622092326912</v>
       </c>
+      <c r="Q15" t="n">
+        <v>0.002266619175598226</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.141251541761293</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.106999909033021</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -41052,6 +41193,15 @@
       <c r="P16" t="n">
         <v>0.188307073113728</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0.002474528494733558</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.08329745874218678</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.133377708409842</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -41104,6 +41254,15 @@
       <c r="P17" t="n">
         <v>-2.233194566287341</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0.01380797361856847</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.1262452705500832</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.214285714285714</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -41156,6 +41315,15 @@
       <c r="P18" t="n">
         <v>-0.8103773586231903</v>
       </c>
+      <c r="Q18" t="n">
+        <v>0.004358594922494044</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3593023319994201</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.132421726383636</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41208,6 +41376,15 @@
       <c r="P19" t="n">
         <v>3.172142313996211</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0.01868640687924359</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2108801241794255</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.202789860506975</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -41260,6 +41437,15 @@
       <c r="P20" t="n">
         <v>0.3392815523803074</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0.01736126687900947</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1256948622636754</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.342771261613486</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -41312,6 +41498,15 @@
       <c r="P21" t="n">
         <v>0.03441511016492327</v>
       </c>
+      <c r="Q21" t="n">
+        <v>0.008515195155274916</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.218485731885954</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.429530080921536</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -41364,6 +41559,15 @@
       <c r="P22" t="n">
         <v>-0.7627713743726641</v>
       </c>
+      <c r="Q22" t="n">
+        <v>0.01260264553985108</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.2259321047710742</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.33360682638661</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -41416,6 +41620,15 @@
       <c r="P23" t="n">
         <v>1.111030642235744</v>
       </c>
+      <c r="Q23" t="n">
+        <v>0.01176623894280151</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3116864441678254</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.409374653714032</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -41468,6 +41681,15 @@
       <c r="P24" t="n">
         <v>0.6992369947913415</v>
       </c>
+      <c r="Q24" t="n">
+        <v>0.009264594389689159</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.2863022905878624</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.377390457994629</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -41520,6 +41742,15 @@
       <c r="P25" t="n">
         <v>1.525202594364361</v>
       </c>
+      <c r="Q25" t="n">
+        <v>0.0133585303562503</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.04672879311130632</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.323438171144943</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -41572,6 +41803,15 @@
       <c r="P26" t="n">
         <v>-0.4147636530768586</v>
       </c>
+      <c r="Q26" t="n">
+        <v>0.008902014107249086</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.02224095277845113</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.313189063447079</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -41624,6 +41864,15 @@
       <c r="P27" t="n">
         <v>0.2882081330190218</v>
       </c>
+      <c r="Q27" t="n">
+        <v>0.007017883900527333</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.1034405317917093</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.287267873914548</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -41676,6 +41925,15 @@
       <c r="P28" t="n">
         <v>0.1757250330031821</v>
       </c>
+      <c r="Q28" t="n">
+        <v>0.006781376526671074</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.04432253074160619</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.324334379347158</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -41728,6 +41986,15 @@
       <c r="P29" t="n">
         <v>0.3840903264205533</v>
       </c>
+      <c r="Q29" t="n">
+        <v>0.0062160707994384</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.1312709917430711</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.64666750170487</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -41780,6 +42047,15 @@
       <c r="P30" t="n">
         <v>-0.29574203433792</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0.006666825379503644</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.09789879407991332</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.50826922522834</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -41832,6 +42108,15 @@
       <c r="P31" t="n">
         <v>0.04112875481250788</v>
       </c>
+      <c r="Q31" t="n">
+        <v>0.006832255575937324</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.1061960163150461</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.575282188635929</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -41884,6 +42169,15 @@
       <c r="P32" t="n">
         <v>0.2548285102542742</v>
       </c>
+      <c r="Q32" t="n">
+        <v>0.006308084108639432</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.1615340036667126</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.651595555492325</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -41936,6 +42230,15 @@
       <c r="P33" t="n">
         <v>-0.3017741170846142</v>
       </c>
+      <c r="Q33" t="n">
+        <v>0.005788767245686176</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.0303569015882237</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.718449644797325</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -41988,6 +42291,15 @@
       <c r="P34" t="n">
         <v>-0.859853262974885</v>
       </c>
+      <c r="Q34" t="n">
+        <v>0.006324114532220059</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.1417218587738271</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.602346289366584</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -42040,6 +42352,15 @@
       <c r="P35" t="n">
         <v>1.626317265089529</v>
       </c>
+      <c r="Q35" t="n">
+        <v>0.006481119676279348</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.04477165494630828</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.611123501533315</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -42092,6 +42413,15 @@
       <c r="P36" t="n">
         <v>0.2065711492552254</v>
       </c>
+      <c r="Q36" t="n">
+        <v>0.006970463307848135</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.03959098759201424</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.527924232204066</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -42144,6 +42474,15 @@
       <c r="P37" t="n">
         <v>0.168437389733997</v>
       </c>
+      <c r="Q37" t="n">
+        <v>0.0108937184976424</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.01119513533924499</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.624405192924382</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -42196,6 +42535,15 @@
       <c r="P38" t="n">
         <v>-0.6162838573686671</v>
       </c>
+      <c r="Q38" t="n">
+        <v>0.005822837619493064</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-0.1024865289957547</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.557860122322594</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -42248,6 +42596,15 @@
       <c r="P39" t="n">
         <v>0.4749281825445728</v>
       </c>
+      <c r="Q39" t="n">
+        <v>0.006677577042158179</v>
+      </c>
+      <c r="R39" t="n">
+        <v>-0.1184047990628848</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.370084953052261</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -42299,6 +42656,15 @@
       </c>
       <c r="P40" t="n">
         <v>0.1963543575166258</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.0064729865862199</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.01353027065824875</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.406528728479568</v>
       </c>
     </row>
   </sheetData>
